--- a/stories/arbres/ATOM-SOC.TRA.001-05.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Papa et Gisèle vont à la gare. Gisèle tient la main de papa. Ils restent avec un adulte. Papa, c'est l'adulte. Un train arrive. Le train fait tchou tchou. Papa dit : c'est un train. C'est le nom du véhicule. Gisèle répète : un train. Ils montent avec papa. Gisèle s'assoit près de papa. Le train roule. Par la fenêtre, Gisèle voit le ciel. Un avion passe. Papa dit : c'est un avion. C'est un autre nom de véhicule. Gisèle dit : un avion. Plus loin, il y a une rivière. Un bateau glisse. Papa dit : c'est un bateau. Gisèle dit : un bateau. Train, avion, bateau. Gisèle nomme. Elle reste avec un adulte.</t>
+          <t>Papa et Gisèle vont à la gare. Gisèle tient la main de papa. Ils restent avec un adulte. Papa, c'est l'adulte. Un train arrive. Le train fait tchou tchou. C'est un train. C'est le nom du véhicule. Gisèle répète : un train. Ils montent avec papa. Gisèle s'assoit près de papa. Le train roule. Par la fenêtre, Gisèle voit le ciel. Un avion passe. C'est un avion. C'est un autre nom de véhicule. Un avion. Plus loin, il y a une rivière. Un bateau glisse. C'est un bateau. Un bateau. Train, avion, bateau. Gisèle nomme. Elle reste avec un adulte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,19 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Papa et Gisèle vont à la gare. Gisèle tient la main de papa. Ils restent avec un adulte. Papa, c'est l'adulte. Un train arrive. Le train fait tchou tchou.
+papa|C'est un train. C'est le nom du véhicule.
+narrateur|Gisèle répète : un train. Ils montent avec papa. Gisèle s'assoit près de papa. Le train roule. Par la fenêtre, Gisèle voit le ciel. Un avion passe.
+papa|C'est un avion. C'est un autre nom de véhicule.
+enfant-f|Un avion. Plus loin, il y a une rivière.
+narrateur|Un bateau glisse.
+papa|C'est un bateau.
+enfant-f|Un bateau. Train, avion, bateau.
+narrateur|Gisèle nomme. Elle reste avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1498,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Gisèle nomme un véhicule. Lequel ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1671,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Gisèle a dit le nom du véhicule. Train. Avion. Bateau. Elle est restée avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1838,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Le train s'arrête. Gisèle donne la main à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2005,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2045,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.TRA.001-05.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.001-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1318,6 +1323,7 @@
 narrateur|Gisèle nomme. Elle reste avec un adulte.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1505,6 +1511,7 @@
           <t>narrateur|Gisèle nomme un véhicule. Lequel ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1676,6 +1683,7 @@
           <t>narrateur|Gisèle a dit le nom du véhicule. Train. Avion. Bateau. Elle est restée avec papa.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1843,6 +1851,7 @@
           <t>narrateur|Le train s'arrête. Gisèle donne la main à papa.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2010,6 +2019,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2028,7 +2038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2052,6 +2062,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2253,6 +2277,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SOC.TRA.001-05.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le train de Gisèle</t>
+          <t>La peluche sous le siège</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mila veut garder sa peluche dans le train. L'ours glisse sous le siège. Papa l'attrape. Elle reste assise.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Papa et Gisèle vont à la gare. Gisèle tient la main de papa. Ils restent avec un adulte. Papa, c'est l'adulte. Un train arrive. Le train fait tchou tchou. C'est un train. C'est le nom du véhicule. Gisèle répète : un train. Ils montent avec papa. Gisèle s'assoit près de papa. Le train roule. Par la fenêtre, Gisèle voit le ciel. Un avion passe. C'est un avion. C'est un autre nom de véhicule. Un avion. Plus loin, il y a une rivière. Un bateau glisse. C'est un bateau. Un bateau. Train, avion, bateau. Gisèle nomme. Elle reste avec un adulte.</t>
+          <t>La laine de la peluche sent le savon. L'ours a une oreille pliée. Le banc du quai est froid. Une feuille sèche tourne. Mila vit ici, avec papa. Tu tiens bien l'ours ? Oui, papa. Le train arrive. En ce moment, le quai vibre. Les lumières du train passent. C'est le train ? Oui. C'est le nom du véhicule. Un train. On monte avec un adulte. Ils montent avec papa. Mila s'assoit près de papa. L'ours est sur ses genoux. Le wagon part tout doux. Les arbres défilent, gris. L'ours regarde dehors. Toi, tu restes assise ? Oui. Le wagon penche un peu. L'ours glisse. Il passe sous le siège. Mon ours ! Tu restes assise, Mila. Papa le prend. Mila reste sur le siège. Ses mains attendent, ouvertes. Papa se baisse, tout près. La laine reparaît. Un peu de poussière vole. Tu restes assise ? Oui. Mila attend, les mains ouvertes. Le wagon roule tout droit. Les arbres sont encore gris. Il a eu peur ? Un petit peu. Maintenant il revient.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Papa et Gisèle vont à la gare. Gisèle tient la main de papa. Ils restent avec un adulte. Papa, c'est l'adulte. Un train arrive. Le train fait tchou tchou. Papa dit : c'est un train. C'est le &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt; du véhicule. Gisèle répète : un train. Ils montent avec papa. Gisèle s'assoit près de papa. Le train roule. Par la fenêtre, Gisèle voit le ciel. Un avion passe. Papa dit : c'est un avion. C'est un autre nom de véhicule. Gisèle dit : un avion. Plus loin, il y a une rivière. Un bateau glisse. Papa dit : c'est un bateau. Gisèle dit : un bateau. Train, avion, bateau. Gisèle nomme. Elle reste avec un adulte.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La laine de la peluche sent le savon. L'ours a une oreille pliée. Le banc du quai est froid. Une feuille sèche tourne. Mila vit ici, avec papa. Tu tiens bien l'ours ? Oui, papa. Le train arrive. En ce moment, le quai vibre. Les lumières du train passent. C'est le train ? Oui. C'est le nom du véhicule. Un train. On monte avec un adulte. Ils montent avec papa. Mila s'assoit près de papa. L'ours est sur ses genoux. Le wagon part tout doux. Les arbres défilent, gris. L'ours regarde dehors. Toi, tu restes assise ? Oui. Le wagon penche un peu. L'ours glisse. Il passe sous le siège. Mon ours ! Tu restes assise, Mila. Papa le prend. Mila reste sur le siège. Ses mains attendent, ouvertes. Papa se baisse, tout près. La laine reparaît. Un peu de poussière vole. Tu restes assise ? Oui. Mila attend, les mains ouvertes. Le wagon roule tout droit. Les arbres sont encore gris. Il a eu peur ? Un petit peu. Maintenant il revient.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,18 +1324,50 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Papa et Gisèle vont à la gare. Gisèle tient la main de papa. Ils restent avec un adulte. Papa, c'est l'adulte. Un train arrive. Le train fait tchou tchou.
-papa|C'est un train. C'est le nom du véhicule.
-narrateur|Gisèle répète : un train. Ils montent avec papa. Gisèle s'assoit près de papa. Le train roule. Par la fenêtre, Gisèle voit le ciel. Un avion passe.
-papa|C'est un avion. C'est un autre nom de véhicule.
-enfant-f|Un avion. Plus loin, il y a une rivière.
-narrateur|Un bateau glisse.
-papa|C'est un bateau.
-enfant-f|Un bateau. Train, avion, bateau.
-narrateur|Gisèle nomme. Elle reste avec un adulte.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La laine de la peluche sent le savon.
+narrateur|L'ours a une oreille pliée.
+narrateur|Le banc du quai est froid.
+narrateur|Une feuille sèche tourne.
+narrateur|Mila vit ici, avec papa.
+papa|Tu tiens bien l'ours ?
+enfant-f|Oui, papa.
+papa|Le train arrive.
+narrateur|En ce moment, le quai vibre.
+narrateur|Les lumières du train passent.
+enfant-f|C'est le train ?
+papa|Oui.
+papa|C'est le nom du véhicule.
+enfant-f|Un train.
+papa|On monte avec un adulte.
+narrateur|Ils montent avec papa.
+narrateur|Mila s'assoit près de papa.
+narrateur|L'ours est sur ses genoux.
+narrateur|Le wagon part tout doux.
+narrateur|Les arbres défilent, gris.
+enfant-f|L'ours regarde dehors.
+papa|Toi, tu restes assise ?
+enfant-f|Oui.
+narrateur|Le wagon penche un peu.
+narrateur|L'ours glisse.
+narrateur|Il passe sous le siège.
+enfant-f|Mon ours !
+papa|Tu restes assise, Mila.
+papa|Papa le prend.
+narrateur|Mila reste sur le siège.
+narrateur|Ses mains attendent, ouvertes.
+narrateur|Papa se baisse, tout près.
+narrateur|La laine reparaît.
+narrateur|Un peu de poussière vole.
+papa|Tu restes assise ?
+enfant-f|Oui.
+narrateur|Mila attend, les mains ouvertes.
+narrateur|Le wagon roule tout droit.
+narrateur|Les arbres sont encore gris.
+enfant-f|Il a eu peur ?
+papa|Un petit peu.
+papa|Maintenant il revient.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1348,12 +1392,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Gisèle nomme un véhicule. Lequel ?</t>
+          <t>Mila nomme le véhicule. Lequel ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Gisèle &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt;me un véhicule. Lequel ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila nomme le véhicule. Lequel ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1368,7 +1412,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>train | avion | bateau | un train</t>
+          <t>train | un train | le train | avion | bateau</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1383,7 +1427,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle a vu un train. Quel véhicule ?</t>
+          <t>Elle a pris le train. Quel véhicule ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1432,7 +1476,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1508,10 +1552,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Gisèle nomme un véhicule. Lequel ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Mila nomme le véhicule.
+narrateur|Lequel ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1536,12 +1580,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Gisèle a dit le nom du véhicule. Train. Avion. Bateau. Elle est restée avec papa.</t>
+          <t>Papa pose l'ours sur les genoux. Merci. Tu es restée assise. Bravo. Mila serre l'oreille pliée. La laine est un peu poussiéreuse. On souffle ? Oui. Elle souffle tout doux. Un fil de poussière danse. Par la fenêtre, le ciel s'ouvre. Tu vois le trait blanc ? Un avion. Oui. C'est un avion. Une rivière apparaît. Un bateau y glisse. Et ça ? Un bateau. Mila reste assise, l'ours contre elle. Tu tiens l'ours, assise ? Oui. L'oreille pliée chatouille le poignet. Mila la lisse, tout doux. Le ciel devient un peu plus bleu. L'ours regarde encore dehors ? Oui. Moi aussi. Ses pieds restent sur le plancher. Le wagon fait un petit toc.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Gisèle a dit le &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt; du véhicule. Train. Avion. Bateau. Elle est restée avec papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa pose l'ours sur les genoux. Merci. Tu es restée assise. Bravo. Mila serre l'oreille pliée. La laine est un peu poussiéreuse. On souffle ? Oui. Elle souffle tout doux. Un fil de poussière danse. Par la fenêtre, le ciel s'ouvre. Tu vois le trait blanc ? Un avion. Oui. C'est un avion. Une rivière apparaît. Un bateau y glisse. Et ça ? Un bateau. Mila reste assise, l'ours contre elle. Tu tiens l'ours, assise ? Oui. L'oreille pliée chatouille le poignet. Mila la lisse, tout doux. Le ciel devient un peu plus bleu. L'ours regarde encore dehors ? Oui. Moi aussi. Ses pieds restent sur le plancher. Le wagon fait un petit toc.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1597,14 +1641,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1680,10 +1724,38 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Gisèle a dit le nom du véhicule. Train. Avion. Bateau. Elle est restée avec papa.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Papa pose l'ours sur les genoux.
+enfant-f|Merci.
+papa|Tu es restée assise.
+papa|Bravo.
+narrateur|Mila serre l'oreille pliée.
+narrateur|La laine est un peu poussiéreuse.
+papa|On souffle ?
+enfant-f|Oui.
+narrateur|Elle souffle tout doux.
+narrateur|Un fil de poussière danse.
+narrateur|Par la fenêtre, le ciel s'ouvre.
+papa|Tu vois le trait blanc ?
+enfant-f|Un avion.
+papa|Oui.
+papa|C'est un avion.
+narrateur|Une rivière apparaît.
+narrateur|Un bateau y glisse.
+papa|Et ça ?
+enfant-f|Un bateau.
+narrateur|Mila reste assise, l'ours contre elle.
+papa|Tu tiens l'ours, assise ?
+enfant-f|Oui.
+narrateur|L'oreille pliée chatouille le poignet.
+narrateur|Mila la lisse, tout doux.
+narrateur|Le ciel devient un peu plus bleu.
+papa|L'ours regarde encore dehors ?
+enfant-f|Oui.
+enfant-f|Moi aussi.
+narrateur|Ses pieds restent sur le plancher.
+narrateur|Le wagon fait un petit toc.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1708,12 +1780,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Le train s'arrête. Gisèle donne la main à papa.</t>
+          <t>Le train ralentit. Les toits redeviennent proches. On arrive. On reste assis encore. L'ours aussi. Le train s'arrête. Maintenant on se lève. Ils se lèvent ensemble. Mila donne la main à papa. L'ours est serré sous le bras. Tu as gardé ta place. Et l'ours.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le train s'arrête. Gisèle donne la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; à papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le train ralentit. Les toits redeviennent proches. On arrive. On reste assis encore. L'ours aussi. Le train s'arrête. Maintenant on se lève. Ils se lèvent ensemble. Mila donne la main à papa. L'ours est serré sous le bras. Tu as gardé ta place. Et l'ours.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1769,14 +1841,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1848,10 +1920,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Le train s'arrête. Gisèle donne la main à papa.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Le train ralentit.
+narrateur|Les toits redeviennent proches.
+papa|On arrive.
+papa|On reste assis encore.
+enfant-f|L'ours aussi.
+narrateur|Le train s'arrête.
+papa|Maintenant on se lève.
+narrateur|Ils se lèvent ensemble.
+narrateur|Mila donne la main à papa.
+narrateur|L'ours est serré sous le bras.
+papa|Tu as gardé ta place.
+enfant-f|Et l'ours.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1876,12 +1958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sur le quai, le vent est frais. L'ours est revenu. Oui. L'oreille pliée sent encore le savon. Mila la frotte contre sa joue. Un fil de laine brille au soleil.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sur le quai, le vent est frais. L'ours est revenu. Oui. L'oreille pliée sent encore le savon. Mila la frotte contre sa joue. Un fil de laine brille au soleil.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1937,14 +2019,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2016,10 +2098,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Sur le quai, le vent est frais.
+enfant-f|L'ours est revenu.
+papa|Oui.
+narrateur|L'oreille pliée sent encore le savon.
+narrateur|Mila la frotte contre sa joue.
+narrateur|Un fil de laine brille au soleil.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2038,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2076,6 +2162,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.TRA.001-05.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.001-05.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>gare et train</t>
+          <t>gare puis wagon, jour gris</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Gisèle, papa</t>
+          <t>Mila, papa</t>
         </is>
       </c>
     </row>
